--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_arica_y_parinacota.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:31</t>
+    <t xml:space="preserve">2026-09-09 20:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_arica_y_parinacota.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:32</t>
+    <t xml:space="preserve">2026-09-18 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
